--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4db1</t>
+          <t>69e82c69836d7d05c9a05533</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4db1</t>
+          <t>69e82c69836d7d05c9a05533</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4db1</t>
+          <t>69efef06ad4799caa7f5e1e6</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6918d0577f059d7aab1b4db1</t>
+          <t>69efef06ad4799caa7f5e1e6</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05533</t>
+          <t>6a04cb3b618f76c4f7b193e4</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c69836d7d05c9a05533</t>
+          <t>6a04cb3b618f76c4f7b193e4</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b193e4</t>
+          <t>6a04cc5b1ef26d534baf3f2b</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3b618f76c4f7b193e4</t>
+          <t>6a04cc5b1ef26d534baf3f2b</t>
         </is>
       </c>
       <c r="B3"/>

--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3f2b</t>
+          <t>6a0614def8d6a2fc74348d75</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>89.93</v>
+        <v>259.96</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1943,7 +1943,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="P2"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>NPI</t>
@@ -2257,7 +2261,9 @@
           <t>01</t>
         </is>
       </c>
-      <c r="CT2"/>
+      <c r="CT2" s="1" t="n">
+        <v>123.0</v>
+      </c>
       <c r="CU2" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -3073,10 +3079,22 @@
       <c r="KY2" s="4" t="n">
         <v>43596.0</v>
       </c>
-      <c r="KZ2"/>
-      <c r="LA2"/>
-      <c r="LB2"/>
-      <c r="LC2"/>
+      <c r="KZ2" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="LA2" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="LB2" s="1" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="LC2" s="1" t="n">
+        <v>22.0</v>
+      </c>
       <c r="LD2" s="3" t="inlineStr">
         <is>
           <t>state regulation 123 was applied during the pricing of this claim</t>
@@ -3092,7 +3110,7 @@
       </c>
       <c r="LG2" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>GRAM</t>
         </is>
       </c>
       <c r="LH2" s="3" t="inlineStr">
@@ -3107,7 +3125,7 @@
       </c>
       <c r="LJ2" s="3" t="inlineStr">
         <is>
-          <t>BM</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="LK2" s="3" t="inlineStr">
@@ -3221,7 +3239,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5b1ef26d534baf3f2b</t>
+          <t>6a0614def8d6a2fc74348d75</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3609,12 +3627,12 @@
       </c>
       <c r="LI3" s="3" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>08</t>
         </is>
       </c>
       <c r="LJ3" s="3" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="LK3" s="3" t="inlineStr">

--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -1872,7 +1872,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348d75</t>
+          <t>6a32cb6497613a0e49909442</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="EZ2" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="FA2" s="4" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="FC2" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>72</t>
         </is>
       </c>
       <c r="FD2" s="4" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="FF2" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>73</t>
         </is>
       </c>
       <c r="FG2" s="4" t="n">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="FI2" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>74</t>
         </is>
       </c>
       <c r="FJ2" s="4" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="FL2" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>75</t>
         </is>
       </c>
       <c r="FM2" s="4" t="n">
@@ -2542,17 +2542,9 @@
       <c r="FN2" s="4" t="n">
         <v>42360.0</v>
       </c>
-      <c r="FO2" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="FP2" s="4" t="n">
-        <v>43093.0</v>
-      </c>
-      <c r="FQ2" s="4" t="n">
-        <v>43100.0</v>
-      </c>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
       <c r="FR2" s="3" t="inlineStr">
         <is>
           <t>03</t>
@@ -3239,7 +3231,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614def8d6a2fc74348d75</t>
+          <t>6a32cb6497613a0e49909442</t>
         </is>
       </c>
       <c r="B3"/>
